--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ95"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2447,45 +2447,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134605151</v>
+        <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>80493</v>
+        <v>93404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Västermarken, Upl</t>
+          <t>76an, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668323</v>
+        <v>668533</v>
       </c>
       <c r="R18" t="n">
-        <v>6695777</v>
+        <v>6695860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,21 +2528,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2558,56 +2543,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605151</t>
+          <t>https://artportalen.se/Sighting/136754218</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134605160</v>
+        <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>93440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Västermarken, Upl</t>
+          <t>76an, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668454</v>
+        <v>668379</v>
       </c>
       <c r="R19" t="n">
-        <v>6695788</v>
+        <v>6695774</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,12 +2614,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,16 +2645,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605160</t>
+          <t>https://artportalen.se/Sighting/136754216</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134605161</v>
+        <v>134605151</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>80493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,39 +2662,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668532</v>
+        <v>668323</v>
       </c>
       <c r="R20" t="n">
-        <v>6695854</v>
+        <v>6695777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,6 +2733,21 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2772,16 +2762,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605161</t>
+          <t>https://artportalen.se/Sighting/134605151</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134605250</v>
+        <v>134605160</v>
       </c>
       <c r="B21" t="n">
-        <v>4782</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,34 +2779,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668350</v>
+        <v>668454</v>
       </c>
       <c r="R21" t="n">
-        <v>6695765</v>
+        <v>6695788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,21 +2855,6 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -2889,16 +2869,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605250</t>
+          <t>https://artportalen.se/Sighting/134605160</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134605140</v>
+        <v>134605161</v>
       </c>
       <c r="B22" t="n">
-        <v>58131</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,16 +2886,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2926,7 +2906,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2915,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668341</v>
+        <v>668532</v>
       </c>
       <c r="R22" t="n">
-        <v>6695788</v>
+        <v>6695854</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,60 +2976,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605140</t>
+          <t>https://artportalen.se/Sighting/134605161</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134605148</v>
+        <v>134605250</v>
       </c>
       <c r="B23" t="n">
-        <v>111471</v>
+        <v>4782</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668643</v>
+        <v>668350</v>
       </c>
       <c r="R23" t="n">
-        <v>6695924</v>
+        <v>6695765</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,6 +3064,21 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3107,48 +3093,44 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605148</t>
+          <t>https://artportalen.se/Sighting/134605250</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134605150</v>
+        <v>134605140</v>
       </c>
       <c r="B24" t="n">
-        <v>111471</v>
+        <v>58131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219711</v>
+        <v>103023</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3157,13 +3139,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668648</v>
+        <v>668341</v>
       </c>
       <c r="R24" t="n">
-        <v>6695919</v>
+        <v>6695788</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,11 +3175,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket rikligt!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,51 +3200,60 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605150</t>
+          <t>https://artportalen.se/Sighting/134605140</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134605192</v>
+        <v>134605148</v>
       </c>
       <c r="B25" t="n">
-        <v>99173</v>
+        <v>111471</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668342</v>
+        <v>668643</v>
       </c>
       <c r="R25" t="n">
-        <v>6695819</v>
+        <v>6695924</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,51 +3311,60 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605192</t>
+          <t>https://artportalen.se/Sighting/134605148</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134605193</v>
+        <v>134605150</v>
       </c>
       <c r="B26" t="n">
-        <v>99173</v>
+        <v>111471</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668330</v>
+        <v>668648</v>
       </c>
       <c r="R26" t="n">
-        <v>6695795</v>
+        <v>6695919</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,6 +3399,11 @@
           <t>2026-06-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mycket rikligt!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3427,13 +3427,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605193</t>
+          <t>https://artportalen.se/Sighting/134605150</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134605194</v>
+        <v>134605192</v>
       </c>
       <c r="B27" t="n">
         <v>99173</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668448</v>
+        <v>668342</v>
       </c>
       <c r="R27" t="n">
-        <v>6695805</v>
+        <v>6695819</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,13 +3529,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605194</t>
+          <t>https://artportalen.se/Sighting/134605192</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134605195</v>
+        <v>134605193</v>
       </c>
       <c r="B28" t="n">
         <v>99173</v>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668434</v>
+        <v>668330</v>
       </c>
       <c r="R28" t="n">
-        <v>6695775</v>
+        <v>6695795</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,13 +3631,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605195</t>
+          <t>https://artportalen.se/Sighting/134605193</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134605196</v>
+        <v>134605194</v>
       </c>
       <c r="B29" t="n">
         <v>99173</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668514</v>
+        <v>668448</v>
       </c>
       <c r="R29" t="n">
-        <v>6695849</v>
+        <v>6695805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,13 +3733,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605196</t>
+          <t>https://artportalen.se/Sighting/134605194</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134605197</v>
+        <v>134605195</v>
       </c>
       <c r="B30" t="n">
         <v>99173</v>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668513</v>
+        <v>668434</v>
       </c>
       <c r="R30" t="n">
-        <v>6695813</v>
+        <v>6695775</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,13 +3835,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605197</t>
+          <t>https://artportalen.se/Sighting/134605195</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134605198</v>
+        <v>134605196</v>
       </c>
       <c r="B31" t="n">
         <v>99173</v>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668693</v>
+        <v>668514</v>
       </c>
       <c r="R31" t="n">
-        <v>6695926</v>
+        <v>6695849</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,16 +3937,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605198</t>
+          <t>https://artportalen.se/Sighting/134605196</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134605255</v>
+        <v>134605197</v>
       </c>
       <c r="B32" t="n">
-        <v>98219</v>
+        <v>99173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219815</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668392</v>
+        <v>668513</v>
       </c>
       <c r="R32" t="n">
-        <v>6695785</v>
+        <v>6695813</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,16 +4039,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605255</t>
+          <t>https://artportalen.se/Sighting/134605197</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134605136</v>
+        <v>134605198</v>
       </c>
       <c r="B33" t="n">
-        <v>99219</v>
+        <v>99173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4056,21 +4056,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668370</v>
+        <v>668693</v>
       </c>
       <c r="R33" t="n">
-        <v>6695784</v>
+        <v>6695926</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4141,16 +4141,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605136</t>
+          <t>https://artportalen.se/Sighting/134605198</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134605137</v>
+        <v>134605255</v>
       </c>
       <c r="B34" t="n">
-        <v>99219</v>
+        <v>98219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,21 +4158,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>219815</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668446</v>
+        <v>668392</v>
       </c>
       <c r="R34" t="n">
-        <v>6695807</v>
+        <v>6695785</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,13 +4243,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605137</t>
+          <t>https://artportalen.se/Sighting/134605255</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134605138</v>
+        <v>134605136</v>
       </c>
       <c r="B35" t="n">
         <v>99219</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668520</v>
+        <v>668370</v>
       </c>
       <c r="R35" t="n">
-        <v>6695819</v>
+        <v>6695784</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4345,16 +4345,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605138</t>
+          <t>https://artportalen.se/Sighting/134605136</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134605216</v>
+        <v>134605137</v>
       </c>
       <c r="B36" t="n">
-        <v>99230</v>
+        <v>99219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4362,21 +4362,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668374</v>
+        <v>668446</v>
       </c>
       <c r="R36" t="n">
-        <v>6695774</v>
+        <v>6695807</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4447,16 +4447,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605216</t>
+          <t>https://artportalen.se/Sighting/134605137</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134605217</v>
+        <v>134605138</v>
       </c>
       <c r="B37" t="n">
-        <v>99230</v>
+        <v>99219</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668466</v>
+        <v>668520</v>
       </c>
       <c r="R37" t="n">
-        <v>6695789</v>
+        <v>6695819</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,13 +4549,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605217</t>
+          <t>https://artportalen.se/Sighting/134605138</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134605218</v>
+        <v>134605216</v>
       </c>
       <c r="B38" t="n">
         <v>99230</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668459</v>
+        <v>668374</v>
       </c>
       <c r="R38" t="n">
-        <v>6695793</v>
+        <v>6695774</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4651,13 +4651,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605218</t>
+          <t>https://artportalen.se/Sighting/134605216</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134605219</v>
+        <v>134605217</v>
       </c>
       <c r="B39" t="n">
         <v>99230</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668441</v>
+        <v>668466</v>
       </c>
       <c r="R39" t="n">
-        <v>6695817</v>
+        <v>6695789</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4753,13 +4753,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605219</t>
+          <t>https://artportalen.se/Sighting/134605217</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134605220</v>
+        <v>134605218</v>
       </c>
       <c r="B40" t="n">
         <v>99230</v>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668552</v>
+        <v>668459</v>
       </c>
       <c r="R40" t="n">
-        <v>6695870</v>
+        <v>6695793</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4855,16 +4855,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605220</t>
+          <t>https://artportalen.se/Sighting/134605218</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134605257</v>
+        <v>134605219</v>
       </c>
       <c r="B41" t="n">
-        <v>108205</v>
+        <v>99230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220083</v>
+        <v>219874</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668331</v>
+        <v>668441</v>
       </c>
       <c r="R41" t="n">
-        <v>6695797</v>
+        <v>6695817</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4957,16 +4957,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605257</t>
+          <t>https://artportalen.se/Sighting/134605219</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134605258</v>
+        <v>134605220</v>
       </c>
       <c r="B42" t="n">
-        <v>108205</v>
+        <v>99230</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220083</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668339</v>
+        <v>668552</v>
       </c>
       <c r="R42" t="n">
-        <v>6695770</v>
+        <v>6695870</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,13 +5059,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605258</t>
+          <t>https://artportalen.se/Sighting/134605220</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134605259</v>
+        <v>134605257</v>
       </c>
       <c r="B43" t="n">
         <v>108205</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668383</v>
+        <v>668331</v>
       </c>
       <c r="R43" t="n">
-        <v>6695798</v>
+        <v>6695797</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,13 +5161,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605259</t>
+          <t>https://artportalen.se/Sighting/134605257</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134605260</v>
+        <v>134605258</v>
       </c>
       <c r="B44" t="n">
         <v>108205</v>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668517</v>
+        <v>668339</v>
       </c>
       <c r="R44" t="n">
-        <v>6695865</v>
+        <v>6695770</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5263,13 +5263,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605260</t>
+          <t>https://artportalen.se/Sighting/134605258</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134605261</v>
+        <v>134605259</v>
       </c>
       <c r="B45" t="n">
         <v>108205</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668647</v>
+        <v>668383</v>
       </c>
       <c r="R45" t="n">
-        <v>6695928</v>
+        <v>6695798</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5365,13 +5365,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605261</t>
+          <t>https://artportalen.se/Sighting/134605259</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134605262</v>
+        <v>134605260</v>
       </c>
       <c r="B46" t="n">
         <v>108205</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668684</v>
+        <v>668517</v>
       </c>
       <c r="R46" t="n">
-        <v>6695915</v>
+        <v>6695865</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5467,60 +5467,51 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605262</t>
+          <t>https://artportalen.se/Sighting/134605260</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134605238</v>
+        <v>134605261</v>
       </c>
       <c r="B47" t="n">
-        <v>99195</v>
+        <v>108205</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668552</v>
+        <v>668647</v>
       </c>
       <c r="R47" t="n">
-        <v>6695817</v>
+        <v>6695928</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,11 +5546,6 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På NÖ sidan av hällmark bland grantätning och äldre tallar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5583,60 +5569,51 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605238</t>
+          <t>https://artportalen.se/Sighting/134605261</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134605239</v>
+        <v>134605262</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>108205</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668556</v>
+        <v>668684</v>
       </c>
       <c r="R48" t="n">
-        <v>6695864</v>
+        <v>6695915</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5671,11 +5648,6 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>I södra slänten i sänka mellan två hällmarker</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5699,43 +5671,43 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605239</t>
+          <t>https://artportalen.se/Sighting/134605262</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134605240</v>
+        <v>134605238</v>
       </c>
       <c r="B49" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5749,10 +5721,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668539</v>
+        <v>668552</v>
       </c>
       <c r="R49" t="n">
-        <v>6695860</v>
+        <v>6695817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,6 +5759,11 @@
           <t>2026-06-23</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På NÖ sidan av hällmark bland grantätning och äldre tallar.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5810,43 +5787,43 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605240</t>
+          <t>https://artportalen.se/Sighting/134605238</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134605241</v>
+        <v>134605239</v>
       </c>
       <c r="B50" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5860,10 +5837,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668541</v>
+        <v>668556</v>
       </c>
       <c r="R50" t="n">
-        <v>6695863</v>
+        <v>6695864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5898,6 +5875,11 @@
           <t>2026-06-23</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I södra slänten i sänka mellan två hällmarker</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5921,13 +5903,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605241</t>
+          <t>https://artportalen.se/Sighting/134605239</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134605242</v>
+        <v>134605240</v>
       </c>
       <c r="B51" t="n">
         <v>106324</v>
@@ -5955,17 +5937,26 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668543</v>
+        <v>668539</v>
       </c>
       <c r="R51" t="n">
-        <v>6695870</v>
+        <v>6695860</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6023,51 +6014,60 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605242</t>
+          <t>https://artportalen.se/Sighting/134605240</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134605114</v>
+        <v>134605241</v>
       </c>
       <c r="B52" t="n">
-        <v>102318</v>
+        <v>106324</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668347</v>
+        <v>668541</v>
       </c>
       <c r="R52" t="n">
-        <v>6695771</v>
+        <v>6695863</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6125,38 +6125,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605114</t>
+          <t>https://artportalen.se/Sighting/134605241</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134605115</v>
+        <v>134605242</v>
       </c>
       <c r="B53" t="n">
-        <v>102318</v>
+        <v>106324</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668369</v>
+        <v>668543</v>
       </c>
       <c r="R53" t="n">
-        <v>6695791</v>
+        <v>6695870</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6227,51 +6227,51 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605115</t>
+          <t>https://artportalen.se/Sighting/134605242</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134605116</v>
+        <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>102318</v>
+        <v>106487</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Västermarken, Upl</t>
+          <t>76an, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668381</v>
+        <v>668524</v>
       </c>
       <c r="R54" t="n">
-        <v>6695791</v>
+        <v>6695857</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6329,13 +6329,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605116</t>
+          <t>https://artportalen.se/Sighting/136754217</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134605117</v>
+        <v>134605114</v>
       </c>
       <c r="B55" t="n">
         <v>102318</v>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668384</v>
+        <v>668347</v>
       </c>
       <c r="R55" t="n">
-        <v>6695802</v>
+        <v>6695771</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6431,13 +6431,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605117</t>
+          <t>https://artportalen.se/Sighting/134605114</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134605118</v>
+        <v>134605115</v>
       </c>
       <c r="B56" t="n">
         <v>102318</v>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668402</v>
+        <v>668369</v>
       </c>
       <c r="R56" t="n">
-        <v>6695813</v>
+        <v>6695791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6533,13 +6533,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605118</t>
+          <t>https://artportalen.se/Sighting/134605115</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134605119</v>
+        <v>134605116</v>
       </c>
       <c r="B57" t="n">
         <v>102318</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668388</v>
+        <v>668381</v>
       </c>
       <c r="R57" t="n">
-        <v>6695765</v>
+        <v>6695791</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6635,13 +6635,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605119</t>
+          <t>https://artportalen.se/Sighting/134605116</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134605120</v>
+        <v>134605117</v>
       </c>
       <c r="B58" t="n">
         <v>102318</v>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668448</v>
+        <v>668384</v>
       </c>
       <c r="R58" t="n">
-        <v>6695805</v>
+        <v>6695802</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,13 +6737,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605120</t>
+          <t>https://artportalen.se/Sighting/134605117</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134605121</v>
+        <v>134605118</v>
       </c>
       <c r="B59" t="n">
         <v>102318</v>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668441</v>
+        <v>668402</v>
       </c>
       <c r="R59" t="n">
-        <v>6695820</v>
+        <v>6695813</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,13 +6839,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605121</t>
+          <t>https://artportalen.se/Sighting/134605118</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134605122</v>
+        <v>134605119</v>
       </c>
       <c r="B60" t="n">
         <v>102318</v>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668476</v>
+        <v>668388</v>
       </c>
       <c r="R60" t="n">
-        <v>6695821</v>
+        <v>6695765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6941,13 +6941,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605122</t>
+          <t>https://artportalen.se/Sighting/134605119</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134605123</v>
+        <v>134605120</v>
       </c>
       <c r="B61" t="n">
         <v>102318</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668496</v>
+        <v>668448</v>
       </c>
       <c r="R61" t="n">
-        <v>6695867</v>
+        <v>6695805</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7043,13 +7043,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605123</t>
+          <t>https://artportalen.se/Sighting/134605120</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134605124</v>
+        <v>134605121</v>
       </c>
       <c r="B62" t="n">
         <v>102318</v>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668516</v>
+        <v>668441</v>
       </c>
       <c r="R62" t="n">
-        <v>6695851</v>
+        <v>6695820</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7145,13 +7145,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605124</t>
+          <t>https://artportalen.se/Sighting/134605121</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134605125</v>
+        <v>134605122</v>
       </c>
       <c r="B63" t="n">
         <v>102318</v>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668513</v>
+        <v>668476</v>
       </c>
       <c r="R63" t="n">
-        <v>6695813</v>
+        <v>6695821</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7247,38 +7247,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605125</t>
+          <t>https://artportalen.se/Sighting/134605122</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134605200</v>
+        <v>134605123</v>
       </c>
       <c r="B64" t="n">
-        <v>98060</v>
+        <v>102318</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668517</v>
+        <v>668496</v>
       </c>
       <c r="R64" t="n">
-        <v>6695869</v>
+        <v>6695867</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7349,38 +7349,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605200</t>
+          <t>https://artportalen.se/Sighting/134605123</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124393159</v>
+        <v>134605124</v>
       </c>
       <c r="B65" t="n">
-        <v>104628</v>
+        <v>102318</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7390,13 +7390,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668678</v>
+        <v>668516</v>
       </c>
       <c r="R65" t="n">
-        <v>6695913</v>
+        <v>6695851</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7451,38 +7451,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124393159</t>
+          <t>https://artportalen.se/Sighting/134605124</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134605141</v>
+        <v>134605125</v>
       </c>
       <c r="B66" t="n">
-        <v>104707</v>
+        <v>102318</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668342</v>
+        <v>668513</v>
       </c>
       <c r="R66" t="n">
-        <v>6695810</v>
+        <v>6695813</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7553,16 +7553,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605141</t>
+          <t>https://artportalen.se/Sighting/134605125</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134605143</v>
+        <v>134605200</v>
       </c>
       <c r="B67" t="n">
-        <v>104707</v>
+        <v>98060</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7570,16 +7570,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668330</v>
+        <v>668517</v>
       </c>
       <c r="R67" t="n">
-        <v>6695795</v>
+        <v>6695869</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7655,16 +7655,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605143</t>
+          <t>https://artportalen.se/Sighting/134605200</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134605144</v>
+        <v>124393159</v>
       </c>
       <c r="B68" t="n">
-        <v>104707</v>
+        <v>104628</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668648</v>
+        <v>668678</v>
       </c>
       <c r="R68" t="n">
-        <v>6695918</v>
+        <v>6695913</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7757,13 +7757,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605144</t>
+          <t>https://artportalen.se/Sighting/124393159</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134605145</v>
+        <v>134605141</v>
       </c>
       <c r="B69" t="n">
         <v>104707</v>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668684</v>
+        <v>668342</v>
       </c>
       <c r="R69" t="n">
-        <v>6695921</v>
+        <v>6695810</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7859,13 +7859,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605145</t>
+          <t>https://artportalen.se/Sighting/134605141</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134605146</v>
+        <v>134605143</v>
       </c>
       <c r="B70" t="n">
         <v>104707</v>
@@ -7900,10 +7900,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668686</v>
+        <v>668330</v>
       </c>
       <c r="R70" t="n">
-        <v>6695923</v>
+        <v>6695795</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7961,13 +7961,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605146</t>
+          <t>https://artportalen.se/Sighting/134605143</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134605147</v>
+        <v>134605144</v>
       </c>
       <c r="B71" t="n">
         <v>104707</v>
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668689</v>
+        <v>668648</v>
       </c>
       <c r="R71" t="n">
-        <v>6695931</v>
+        <v>6695918</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8063,16 +8063,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605147</t>
+          <t>https://artportalen.se/Sighting/134605144</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134605263</v>
+        <v>134605145</v>
       </c>
       <c r="B72" t="n">
-        <v>101403</v>
+        <v>104707</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8080,21 +8080,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8104,10 +8104,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668344</v>
+        <v>668684</v>
       </c>
       <c r="R72" t="n">
-        <v>6695826</v>
+        <v>6695921</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8165,16 +8165,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605263</t>
+          <t>https://artportalen.se/Sighting/134605145</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134605264</v>
+        <v>134605146</v>
       </c>
       <c r="B73" t="n">
-        <v>101403</v>
+        <v>104707</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8182,21 +8182,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668376</v>
+        <v>668686</v>
       </c>
       <c r="R73" t="n">
-        <v>6695785</v>
+        <v>6695923</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8267,16 +8267,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605264</t>
+          <t>https://artportalen.se/Sighting/134605146</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134605265</v>
+        <v>134605147</v>
       </c>
       <c r="B74" t="n">
-        <v>101403</v>
+        <v>104707</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8284,21 +8284,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668449</v>
+        <v>668689</v>
       </c>
       <c r="R74" t="n">
-        <v>6695803</v>
+        <v>6695931</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8369,13 +8369,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605265</t>
+          <t>https://artportalen.se/Sighting/134605147</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134605266</v>
+        <v>134605263</v>
       </c>
       <c r="B75" t="n">
         <v>101403</v>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668480</v>
+        <v>668344</v>
       </c>
       <c r="R75" t="n">
-        <v>6695851</v>
+        <v>6695826</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8471,13 +8471,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605266</t>
+          <t>https://artportalen.se/Sighting/134605263</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134605267</v>
+        <v>134605264</v>
       </c>
       <c r="B76" t="n">
         <v>101403</v>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668497</v>
+        <v>668376</v>
       </c>
       <c r="R76" t="n">
-        <v>6695866</v>
+        <v>6695785</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8573,13 +8573,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605267</t>
+          <t>https://artportalen.se/Sighting/134605264</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134605268</v>
+        <v>134605265</v>
       </c>
       <c r="B77" t="n">
         <v>101403</v>
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668514</v>
+        <v>668449</v>
       </c>
       <c r="R77" t="n">
-        <v>6695849</v>
+        <v>6695803</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8675,13 +8675,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605268</t>
+          <t>https://artportalen.se/Sighting/134605265</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134605270</v>
+        <v>134605266</v>
       </c>
       <c r="B78" t="n">
         <v>101403</v>
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668517</v>
+        <v>668480</v>
       </c>
       <c r="R78" t="n">
-        <v>6695818</v>
+        <v>6695851</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8777,13 +8777,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605270</t>
+          <t>https://artportalen.se/Sighting/134605266</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134605271</v>
+        <v>134605267</v>
       </c>
       <c r="B79" t="n">
         <v>101403</v>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668519</v>
+        <v>668497</v>
       </c>
       <c r="R79" t="n">
-        <v>6695868</v>
+        <v>6695866</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8879,13 +8879,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605271</t>
+          <t>https://artportalen.se/Sighting/134605267</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134605272</v>
+        <v>134605268</v>
       </c>
       <c r="B80" t="n">
         <v>101403</v>
@@ -8920,10 +8920,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668639</v>
+        <v>668514</v>
       </c>
       <c r="R80" t="n">
-        <v>6695922</v>
+        <v>6695849</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8981,13 +8981,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605272</t>
+          <t>https://artportalen.se/Sighting/134605268</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134605273</v>
+        <v>134605270</v>
       </c>
       <c r="B81" t="n">
         <v>101403</v>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668649</v>
+        <v>668517</v>
       </c>
       <c r="R81" t="n">
-        <v>6695908</v>
+        <v>6695818</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9083,13 +9083,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605273</t>
+          <t>https://artportalen.se/Sighting/134605270</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134605274</v>
+        <v>134605271</v>
       </c>
       <c r="B82" t="n">
         <v>101403</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668693</v>
+        <v>668519</v>
       </c>
       <c r="R82" t="n">
-        <v>6695926</v>
+        <v>6695868</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,13 +9185,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605274</t>
+          <t>https://artportalen.se/Sighting/134605271</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134605275</v>
+        <v>134605272</v>
       </c>
       <c r="B83" t="n">
         <v>101403</v>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668688</v>
+        <v>668639</v>
       </c>
       <c r="R83" t="n">
-        <v>6695941</v>
+        <v>6695922</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9287,16 +9287,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605275</t>
+          <t>https://artportalen.se/Sighting/134605272</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134605201</v>
+        <v>134605273</v>
       </c>
       <c r="B84" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9304,21 +9304,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668326</v>
+        <v>668649</v>
       </c>
       <c r="R84" t="n">
-        <v>6695768</v>
+        <v>6695908</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9389,16 +9389,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605201</t>
+          <t>https://artportalen.se/Sighting/134605273</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134605202</v>
+        <v>134605274</v>
       </c>
       <c r="B85" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9406,21 +9406,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668405</v>
+        <v>668693</v>
       </c>
       <c r="R85" t="n">
-        <v>6695781</v>
+        <v>6695926</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9491,16 +9491,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605202</t>
+          <t>https://artportalen.se/Sighting/134605274</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134605203</v>
+        <v>134605275</v>
       </c>
       <c r="B86" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668432</v>
+        <v>668688</v>
       </c>
       <c r="R86" t="n">
-        <v>6695805</v>
+        <v>6695941</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9593,13 +9593,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605203</t>
+          <t>https://artportalen.se/Sighting/134605275</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134605204</v>
+        <v>134605201</v>
       </c>
       <c r="B87" t="n">
         <v>99001</v>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668480</v>
+        <v>668326</v>
       </c>
       <c r="R87" t="n">
-        <v>6695864</v>
+        <v>6695768</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9695,13 +9695,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605204</t>
+          <t>https://artportalen.se/Sighting/134605201</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134605205</v>
+        <v>134605202</v>
       </c>
       <c r="B88" t="n">
         <v>99001</v>
@@ -9736,10 +9736,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668514</v>
+        <v>668405</v>
       </c>
       <c r="R88" t="n">
-        <v>6695849</v>
+        <v>6695781</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9797,13 +9797,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605205</t>
+          <t>https://artportalen.se/Sighting/134605202</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134605206</v>
+        <v>134605203</v>
       </c>
       <c r="B89" t="n">
         <v>99001</v>
@@ -9838,10 +9838,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668515</v>
+        <v>668432</v>
       </c>
       <c r="R89" t="n">
-        <v>6695864</v>
+        <v>6695805</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9899,13 +9899,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605206</t>
+          <t>https://artportalen.se/Sighting/134605203</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134605207</v>
+        <v>134605204</v>
       </c>
       <c r="B90" t="n">
         <v>99001</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668535</v>
+        <v>668480</v>
       </c>
       <c r="R90" t="n">
-        <v>6695872</v>
+        <v>6695864</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10001,13 +10001,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605207</t>
+          <t>https://artportalen.se/Sighting/134605204</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134605208</v>
+        <v>134605205</v>
       </c>
       <c r="B91" t="n">
         <v>99001</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668594</v>
+        <v>668514</v>
       </c>
       <c r="R91" t="n">
-        <v>6695860</v>
+        <v>6695849</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10103,13 +10103,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605208</t>
+          <t>https://artportalen.se/Sighting/134605205</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134605209</v>
+        <v>134605206</v>
       </c>
       <c r="B92" t="n">
         <v>99001</v>
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668648</v>
+        <v>668515</v>
       </c>
       <c r="R92" t="n">
-        <v>6695919</v>
+        <v>6695864</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10205,13 +10205,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605209</t>
+          <t>https://artportalen.se/Sighting/134605206</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134605211</v>
+        <v>134605207</v>
       </c>
       <c r="B93" t="n">
         <v>99001</v>
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>668684</v>
+        <v>668535</v>
       </c>
       <c r="R93" t="n">
-        <v>6695915</v>
+        <v>6695872</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10307,13 +10307,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605211</t>
+          <t>https://artportalen.se/Sighting/134605207</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134605212</v>
+        <v>134605208</v>
       </c>
       <c r="B94" t="n">
         <v>99001</v>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668671</v>
+        <v>668594</v>
       </c>
       <c r="R94" t="n">
-        <v>6695935</v>
+        <v>6695860</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10409,38 +10409,38 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134605212</t>
+          <t>https://artportalen.se/Sighting/134605208</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134605199</v>
+        <v>134605209</v>
       </c>
       <c r="B95" t="n">
-        <v>103482</v>
+        <v>99001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223246</v>
+        <v>223049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668442</v>
+        <v>668648</v>
       </c>
       <c r="R95" t="n">
-        <v>6695764</v>
+        <v>6695919</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10488,11 +10488,6 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ca 1 m hög</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10515,6 +10510,317 @@
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134605209</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134605211</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>668684</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6695915</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134605211</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>134605212</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>668671</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6695935</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134605212</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134605199</v>
+      </c>
+      <c r="B98" t="n">
+        <v>103482</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>668442</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6695764</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ca 1 m hög</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134605199</t>
         </is>
@@ -10616,6 +10922,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 26552-2026 artfynd.xlsx
+++ b/artfynd/A 26552-2026 artfynd.xlsx
@@ -2450,7 +2450,7 @@
         <v>136754218</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136754216</v>
       </c>
       <c r="B19" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136754217</v>
       </c>
       <c r="B54" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
